--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -48741,6 +48741,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2104">
+      <c r="A2104" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="G2104" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -48764,6 +48764,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2105" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -48787,6 +48787,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2106">
+      <c r="A2106" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2106" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -48810,6 +48810,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2107" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -48651,7 +48651,7 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2100" t="n">
         <v>0</v>
@@ -48674,22 +48674,22 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2101" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C2101" t="n">
-        <v>0.595000028610229</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="D2101" t="n">
-        <v>0.595000028610229</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="E2101" t="n">
-        <v>0.595000028610229</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.595000028610229</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="G2101" t="s">
         <v>7</v>
@@ -48697,22 +48697,22 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2102" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C2102" t="n">
-        <v>0.584999978542328</v>
+        <v>0.595000028610229</v>
       </c>
       <c r="D2102" t="n">
-        <v>0.584999978542328</v>
+        <v>0.595000028610229</v>
       </c>
       <c r="E2102" t="n">
-        <v>0.584999978542328</v>
+        <v>0.595000028610229</v>
       </c>
       <c r="F2102" t="n">
-        <v>0.584999978542328</v>
+        <v>0.595000028610229</v>
       </c>
       <c r="G2102" t="s">
         <v>7</v>
@@ -48720,22 +48720,22 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2103" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="C2103" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="D2103" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="E2103" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="F2103" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="G2103" t="s">
         <v>7</v>
@@ -48743,22 +48743,22 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2104" t="n">
         <v>1000</v>
       </c>
       <c r="C2104" t="n">
-        <v>0.584999978542328</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="D2104" t="n">
-        <v>0.584999978542328</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="E2104" t="n">
-        <v>0.584999978542328</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="F2104" t="n">
-        <v>0.584999978542328</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="G2104" t="s">
         <v>7</v>
@@ -48766,22 +48766,22 @@
     </row>
     <row r="2105">
       <c r="A2105" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2105" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C2105" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="D2105" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="E2105" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="F2105" t="n">
-        <v>0.574999988079071</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="G2105" t="s">
         <v>7</v>
@@ -48789,10 +48789,10 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2106" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="C2106" t="n">
         <v>0.574999988079071</v>
@@ -48812,19 +48812,19 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2107" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="C2107" t="n">
-        <v>0.579999983310699</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="D2107" t="n">
         <v>0.574999988079071</v>
       </c>
       <c r="E2107" t="n">
-        <v>0.579999983310699</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="F2107" t="n">
         <v>0.574999988079071</v>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -48833,6 +48833,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2108">
+      <c r="A2108" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2108" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2109" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -55261,6 +55261,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2112">
+      <c r="A2112" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="H2112" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -55287,6 +55287,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2113">
+      <c r="A2113" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="H2113" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -55313,6 +55313,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2114">
+      <c r="A2114" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="H2114" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -55391,6 +55391,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2117">
+      <c r="A2117" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="H2117" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -49125,8 +49125,31 @@
       <c r="E2120" t="n">
         <v>0.569999992847443</v>
       </c>
-      <c r="F2120"/>
+      <c r="F2120" t="n">
+        <v>0.569999992847443</v>
+      </c>
       <c r="G2120" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2121"/>
+      <c r="G2121" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -49148,8 +49148,31 @@
       <c r="E2121" t="n">
         <v>0.579999983310699</v>
       </c>
-      <c r="F2121"/>
+      <c r="F2121" t="n">
+        <v>0.574999988079071</v>
+      </c>
       <c r="G2121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2122"/>
+      <c r="G2122" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -49171,8 +49171,31 @@
       <c r="E2122" t="n">
         <v>0.579999983310699</v>
       </c>
-      <c r="F2122"/>
+      <c r="F2122" t="n">
+        <v>0.574999988079071</v>
+      </c>
       <c r="G2122" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2123"/>
+      <c r="G2123" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -49194,8 +49194,31 @@
       <c r="E2123" t="n">
         <v>0.574999988079071</v>
       </c>
-      <c r="F2123"/>
+      <c r="F2123" t="n">
+        <v>0.574999988079071</v>
+      </c>
       <c r="G2123" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="F2124"/>
+      <c r="G2124" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -49224,6 +49224,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2125">
+      <c r="A2125" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="G2125" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -55677,6 +55677,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2128">
+      <c r="A2128" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2128" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="H2128" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -55703,6 +55703,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2129" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2129" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62119,6 +62119,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2130">
+      <c r="A2130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2130" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2130" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="E2130" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="F2130" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="G2130" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="H2130" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I2130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2131" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2131" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G2131" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="H2131" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I2131" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62177,6 +62177,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2132">
+      <c r="A2132" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2132" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2132" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="G2132" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="H2132" t="n">
+        <v>24500</v>
+      </c>
+      <c r="I2132" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62206,6 +62206,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2133">
+      <c r="A2133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2133" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2133" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="G2133" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="H2133" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I2133" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62235,6 +62235,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2134">
+      <c r="A2134" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2134" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2134" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="G2134" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="H2134" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I2134" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62264,6 +62264,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2135">
+      <c r="A2135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2135" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2135" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="G2135" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="H2135" t="n">
+        <v>500</v>
+      </c>
+      <c r="I2135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2136" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2136" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="G2136" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="H2136" t="n">
+        <v>500</v>
+      </c>
+      <c r="I2136" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62322,6 +62322,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2137">
+      <c r="A2137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2137" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="G2137" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="H2137" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I2137" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62351,6 +62351,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2138">
+      <c r="A2138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2138" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2138" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2138" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I2138" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRAL.MI.xlsx
+++ b/data/GRAL.MI.xlsx
@@ -62380,6 +62380,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2139">
+      <c r="A2139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2139" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2139" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="G2139" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="H2139" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I2139" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
